--- a/examples/excel/charts/charts-line.xlsx
+++ b/examples/excel/charts/charts-line.xlsx
@@ -3,13 +3,14 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Line Fundamentals" sheetId="2" r:id="R24c97b32ff404052"/>
-    <x:sheet name="2-Line Styles" sheetId="3" r:id="Rd4cc8124281e4f94"/>
-    <x:sheet name="3-Line Variants" sheetId="4" r:id="R179dea0c8282414f"/>
-    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R3b0ab19ce75042dd"/>
-    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="R9f13b691275b40be"/>
-    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="Rab7a8a2eb6af40ed"/>
-    <x:sheet name="7-Line Elements" sheetId="8" r:id="R98d15ac20ad94cd8"/>
+    <x:sheet name="1-Line Fundamentals" sheetId="2" r:id="R6c8d488a8f9d4033"/>
+    <x:sheet name="2-Line Styles" sheetId="3" r:id="R4c99dd598bc6496c"/>
+    <x:sheet name="3-Line Variants" sheetId="4" r:id="R486ebd1dd09b4660"/>
+    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R0f79507c2e5944e4"/>
+    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="Rc5029a96510a4ff4"/>
+    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="Rdb7425d8efc94a73"/>
+    <x:sheet name="7-Line Elements" sheetId="8" r:id="Rb4283abf8c1244bb"/>
+    <x:sheet name="8-Axis Extras" sheetId="9" r:id="R0dd09002bb794612"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -225,7 +226,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -777,7 +777,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -1271,6 +1270,7 @@
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:line3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -1304,6 +1304,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -1754,7 +1763,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -2311,16 +2319,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
-              <a:solidFill>
-                <a:srgbClr val="D0D0D0"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:minorGridlines>
           <c:spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3810">
@@ -2331,7 +2330,7 @@
             </a:ln>
           </c:spPr>
         </c:minorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2343,6 +2342,14 @@
             <a:prstDash val="solid"/>
           </a:ln>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr/>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -3178,6 +3185,14 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
@@ -3755,7 +3770,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -4400,7 +4414,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -4553,6 +4566,7 @@
           </c:val>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4635,6 +4649,15 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:axId val="3"/>
         <c:axId val="4"/>
@@ -4732,7 +4755,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -5291,7 +5314,6 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:marker val="1"/>
         <c:smooth val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -5608,7 +5630,7 @@
             <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="800" b="0">
+                <a:defRPr sz="800">
                   <a:solidFill>
                     <a:srgbClr val="666666"/>
                   </a:solidFill>
@@ -6851,9 +6873,10 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:gapDepth val="300"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:gapDepth val="300"/>
+        <c:axId val="3"/>
       </c:line3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -6887,6 +6910,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -6900,6 +6932,148 @@
       <a:srgbClr val="F5F5F5"/>
     </a:solidFill>
   </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>crossesAt — axis baseline at 50</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Score</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E75B6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+          </c:marker>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>Jan</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Feb</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Mar</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Apr</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>May</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Jun</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Jul</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>65</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>55</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>90</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>70</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crossesAt val="50"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
 </c:chartSpace>
 </file>
 
@@ -7435,6 +7609,404 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart30.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>dispBlanksAs=span (connect gaps)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="548235"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+          </c:marker>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>Jan</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Feb</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Mar</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Apr</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>May</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>130</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>160</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="span"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>dispBlanksAs=zero + crossesAt=0</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+          </c:marker>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>Jan</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Feb</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Mar</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Apr</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>May</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>130</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>160</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crossesAt val="0"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>crosses=max (value axis at far end)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Index</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+          </c:spPr>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>Mon</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Tue</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Wed</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Thu</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Fri</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Sat</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Sun</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="7"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>52</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>75</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>68</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>90</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:chart>
@@ -7549,7 +8121,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -8062,7 +8633,6 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:marker val="1"/>
         <c:smooth val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -8359,7 +8929,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -9392,7 +9961,6 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:marker val="1"/>
         <c:smooth val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -9888,7 +10456,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -9997,7 +10564,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a232e0d5cca44a8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c7aaf7bbe484f09"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10027,7 +10594,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d028fcae4594fc2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bb1ee656e004c3a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10057,7 +10624,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re9a7eab82ea94cc8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redb9511d7c0e4d9d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10087,7 +10654,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7db34226703b4f29"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R455cea3f2e194acf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10122,7 +10689,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1a484f6974674d0a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1686326314ab4db1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10152,7 +10719,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rec0dff9761ea4a1c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0e48c25aab4462a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10182,7 +10749,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8887e528b654c1c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf24858f4e37a4dc8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10212,7 +10779,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb54bf6adf35a4658"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra23aac3af724432e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10247,7 +10814,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c557bfe6b8b42b8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b2d5f8be3b54c66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10277,7 +10844,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R05bf2db6710b453e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf455eebaaa94452c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10307,7 +10874,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8f5e35deb72498a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8ad2a55a1565498f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10337,7 +10904,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6864ace4f434fa7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8729128951c4cd3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10372,7 +10939,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R713d04dadc424f16"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R585fa3ff8b544bb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10402,7 +10969,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R34b9f1ebfc85406c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29304db882e14bc3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10432,7 +10999,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re2f4d66f4aed4411"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbcaa9aaf4f0f4c65"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10462,7 +11029,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R66ba99f7eec1447c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1fb8439c729a476d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10497,7 +11064,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf362b5e9910484d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7de0420ecdfb4022"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10527,7 +11094,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2dbb279b8e634812"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf7e55804fefa43b4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10557,7 +11124,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R709b0fda82594d61"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95ea5694838a49ad"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10587,7 +11154,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9fd382b1e1b84731"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33b7f4eccaf248b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10622,7 +11189,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf63ba82354794c48"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd852874e74744ecb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10652,7 +11219,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56a6d3312835445e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38213bb896364678"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10682,7 +11249,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R607c0fb91dda4b61"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfd6cb014878c47d1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10712,7 +11279,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e8e3c7da2224d3d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95f49e074c2e4b11"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10747,7 +11314,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rddf220fd100e4113"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re1db44f913b9435c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10777,7 +11344,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc2e4a043ce70430d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a0f9e739194d33"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10807,7 +11374,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd46e119959794e2f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3602d8b741f243c2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10837,7 +11404,132 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3dec818039d84265"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c6f44e29c9b4f9c"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="crossesAt — axis baseline at 50"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb46d973c4e5d4707"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="dispBlanksAs=span (connect gaps)"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78b9c98ba75c4f2e"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="dispBlanksAs=zero + crossesAt=0"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redc1cefc97eb4b48"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="crosses=max (value axis at far end)"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29fc3da1b0a2446b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11077,48 +11769,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb700e86283954b52"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f8947c654374516"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1dc65648ad74637"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca9d551801e46d7"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bd62a4e93d54c83"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf14950f47f34265"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe183d653c074707"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9632bdbe854730"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb58f90e02cb4068"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd22d1ebf2d40f9"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330f9cefc45e430e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba965dc4e91e4909"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6214f4cac944f59"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5661d60d16f04bb9"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cb0f41c87b84584"/>
 </x:worksheet>
 </file>